--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="511">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Aspect du cholestérol</t>
+    <t>Cholestérol - aspect</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -871,7 +868,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
@@ -903,13 +900,41 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x].id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
+    <t>Observation.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
+  </si>
+  <si>
+    <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-6
 </t>
   </si>
   <si>
+    <t>value.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.dataAbsentReason.id</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -922,7 +947,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.value[x].extension</t>
+    <t>Observation.dataAbsentReason.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -941,172 +966,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>Observation.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>Observation.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>mmol/L</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x].system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>http://unitsofmeasure.org</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
-  </si>
-  <si>
-    <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-6
-</t>
-  </si>
-  <si>
-    <t>value.nullFlavor</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason.id</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason.extension</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason.coding</t>
   </si>
   <si>
@@ -1476,7 +1335,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}mes-ir:L'intervalle de référence est obligatoire dans le cas où la donnée provient d'un compte rendu de biologie. {null}</t>
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1882,21 +1741,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2070,7 +1914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AP62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
@@ -2098,7 +1942,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2244,7 +2088,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2364,7 +2208,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -2484,7 +2328,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -2602,7 +2446,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -2722,7 +2566,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -2842,7 +2686,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -2962,7 +2806,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>129</v>
       </c>
@@ -3082,7 +2926,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>137</v>
       </c>
@@ -3202,7 +3046,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -3324,7 +3168,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3444,7 +3288,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -3564,7 +3408,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>168</v>
       </c>
@@ -3684,7 +3528,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>177</v>
       </c>
@@ -3806,7 +3650,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>190</v>
       </c>
@@ -3928,7 +3772,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>200</v>
       </c>
@@ -4050,7 +3894,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>216</v>
       </c>
@@ -4172,7 +4016,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>226</v>
       </c>
@@ -4292,7 +4136,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>232</v>
       </c>
@@ -4414,7 +4258,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>243</v>
       </c>
@@ -4536,7 +4380,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>254</v>
       </c>
@@ -4656,7 +4500,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>262</v>
       </c>
@@ -4776,7 +4620,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>271</v>
       </c>
@@ -4898,7 +4742,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>282</v>
       </c>
@@ -4926,16 +4770,20 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4959,13 +4807,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4983,7 +4831,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4992,10 +4840,10 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5004,10 +4852,10 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5016,23 +4864,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5044,17 +4892,15 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>140</v>
+        <v>293</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5091,31 +4937,31 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5127,7 +4973,7 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5136,23 +4982,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5161,23 +5007,21 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>295</v>
+        <v>139</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>296</v>
+        <v>140</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5213,31 +5057,31 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5246,10 +5090,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5258,7 +5102,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>303</v>
       </c>
@@ -5274,36 +5118,36 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>113</v>
+        <v>304</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q27" t="s" s="2">
-        <v>307</v>
-      </c>
+      <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5323,37 +5167,37 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AA27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5368,24 +5212,24 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5393,7 +5237,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
@@ -5405,21 +5249,19 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>316</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5428,7 +5270,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5467,7 +5309,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5479,7 +5321,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5488,10 +5330,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5500,23 +5342,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5525,21 +5367,21 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>140</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5548,7 +5390,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5575,31 +5417,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5608,10 +5450,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5620,12 +5462,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5648,19 +5490,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5670,7 +5512,7 @@
         <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>82</v>
@@ -5709,7 +5551,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5730,10 +5572,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5742,12 +5584,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5767,23 +5609,21 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5807,13 +5647,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5831,7 +5671,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5840,7 +5680,7 @@
         <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>105</v>
@@ -5852,10 +5692,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>136</v>
+        <v>327</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5864,12 +5704,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5877,7 +5717,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -5889,19 +5729,21 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>283</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5949,7 +5791,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5961,7 +5803,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5970,10 +5812,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5982,23 +5824,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6007,21 +5849,21 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>140</v>
+        <v>337</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6057,31 +5899,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6090,10 +5932,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>287</v>
+        <v>342</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6102,12 +5944,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6118,7 +5960,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6130,19 +5972,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6191,13 +6033,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6212,10 +6054,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6224,12 +6066,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6249,19 +6091,23 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6309,7 +6155,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>357</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6321,7 +6167,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6330,10 +6176,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>287</v>
+        <v>359</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6342,16 +6188,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>138</v>
+        <v>361</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6370,18 +6216,20 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>140</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>363</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6405,31 +6253,31 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>360</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6441,33 +6289,33 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>287</v>
+        <v>370</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6475,10 +6323,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6487,22 +6335,22 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>373</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6551,13 +6399,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6572,10 +6420,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6584,12 +6432,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6609,19 +6457,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>283</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6647,13 +6495,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6671,7 +6519,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6689,27 +6537,27 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6717,7 +6565,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
@@ -6729,20 +6577,22 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6767,13 +6617,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6791,7 +6641,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6812,10 +6662,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6824,12 +6674,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6849,21 +6699,21 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>283</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6911,7 +6761,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6929,27 +6779,27 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6969,23 +6819,21 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7033,7 +6881,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7051,27 +6899,27 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7082,7 +6930,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7091,22 +6939,22 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>283</v>
+        <v>418</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7155,19 +7003,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>423</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7176,10 +7024,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7188,23 +7036,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7216,20 +7064,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>407</v>
+        <v>293</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7253,13 +7097,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7277,49 +7121,49 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>415</v>
+        <v>296</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7338,20 +7182,18 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>418</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>140</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>298</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7399,7 +7241,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>302</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7411,7 +7253,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7420,10 +7262,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>424</v>
+        <v>296</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7432,46 +7274,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7495,13 +7339,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7519,45 +7363,45 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7580,20 +7424,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>191</v>
+        <v>434</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>439</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7617,13 +7457,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7641,7 +7481,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7650,7 +7490,7 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>105</v>
@@ -7662,10 +7502,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7674,12 +7514,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7702,17 +7542,15 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7761,7 +7599,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7770,7 +7608,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7779,27 +7617,27 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7822,18 +7660,20 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>454</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7857,13 +7697,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7881,7 +7721,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7899,27 +7739,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7927,13 +7767,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
@@ -7942,19 +7782,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>463</v>
+        <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7979,13 +7819,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8003,7 +7843,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8015,19 +7855,19 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>468</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>470</v>
+        <v>370</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8036,12 +7876,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8064,16 +7904,18 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>283</v>
+        <v>461</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>284</v>
+        <v>462</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>285</v>
+        <v>463</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8121,7 +7963,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>286</v>
+        <v>460</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8133,7 +7975,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8145,7 +7987,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>287</v>
+        <v>465</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8154,23 +7996,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8182,17 +8024,15 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>140</v>
+        <v>467</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8241,19 +8081,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>293</v>
+        <v>466</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8262,10 +8102,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>287</v>
+        <v>469</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8274,48 +8114,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>139</v>
+        <v>471</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8363,7 +8201,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8375,7 +8213,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8384,10 +8222,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>136</v>
+        <v>476</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8396,12 +8234,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8409,10 +8247,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8421,18 +8259,20 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8481,16 +8321,16 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8502,24 +8342,24 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AN53" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8530,7 +8370,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8539,19 +8379,23 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>479</v>
+        <v>418</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8599,16 +8443,16 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8620,10 +8464,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8632,12 +8476,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8648,7 +8492,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8660,20 +8504,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>490</v>
+        <v>293</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8697,13 +8537,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8721,7 +8561,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>489</v>
+        <v>295</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8733,19 +8573,19 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>415</v>
+        <v>296</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8754,23 +8594,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8782,20 +8622,18 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>500</v>
+        <v>298</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8819,13 +8657,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8843,7 +8681,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>498</v>
+        <v>302</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8855,19 +8693,19 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>415</v>
+        <v>296</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8876,45 +8714,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>506</v>
+        <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>507</v>
+        <v>430</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>509</v>
+        <v>148</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8963,19 +8803,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>505</v>
+        <v>432</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -8987,7 +8827,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>510</v>
+        <v>136</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8996,12 +8836,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9009,7 +8849,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
@@ -9021,19 +8861,23 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>283</v>
+        <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9057,13 +8901,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9081,10 +8925,10 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>93</v>
@@ -9099,27 +8943,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>483</v>
+        <v>212</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>514</v>
+        <v>213</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9130,7 +8974,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9142,18 +8986,20 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>518</v>
+        <v>274</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9201,13 +9047,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9219,27 +9065,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>520</v>
+        <v>279</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>521</v>
+        <v>280</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9250,7 +9096,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9259,21 +9105,23 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>523</v>
+        <v>191</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9297,13 +9145,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9321,16 +9169,16 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9342,10 +9190,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>520</v>
+        <v>136</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>527</v>
+        <v>291</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9354,16 +9202,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9379,22 +9227,22 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>529</v>
+        <v>362</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>530</v>
+        <v>363</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>531</v>
+        <v>364</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>532</v>
+        <v>365</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9419,13 +9267,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9443,7 +9291,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9461,27 +9309,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>533</v>
+        <v>369</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>534</v>
+        <v>370</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>535</v>
+        <v>508</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>535</v>
+        <v>508</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9492,7 +9340,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9504,16 +9352,20 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>284</v>
+        <v>509</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9561,19 +9413,19 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>286</v>
+        <v>508</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9582,889 +9434,19 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>287</v>
+        <v>425</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP69" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP69">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -545,7 +545,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -628,7 +628,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -671,7 +671,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -695,7 +695,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -749,7 +749,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -840,7 +840,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -922,7 +922,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1161,7 +1161,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1217,7 +1217,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1259,7 +1259,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1287,7 +1287,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1367,7 +1367,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1417,7 +1417,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1450,7 +1450,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1487,7 +1487,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1509,7 +1509,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1924,7 +1924,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="564">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -339,13 +339,190 @@
 </t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -441,28 +618,66 @@
     <t>Observation.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:supportingInfo</t>
+  </si>
+  <si>
+    <t>supportingInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-supportingInfo}
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>Other information that may be relevant to this event.</t>
+  </si>
+  <si>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Valeur d'origine de la donnée. Cette extension est présente uniquement si le résultat contenu dans Observation.value provient d'une conversion (par ex. g/L converti en mmol/L)</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -665,9 +880,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
@@ -695,7 +907,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -749,7 +961,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -815,35 +1027,31 @@
     <t>Observation.issued</t>
   </si>
   <si>
-    <t xml:space="preserve">instant
+    <t>Date/Time this version was made available</t>
+  </si>
+  <si>
+    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
     <t>Who is responsible for the observation</t>
   </si>
   <si>
@@ -866,10 +1074,6 @@
   </si>
   <si>
     <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Actual result</t>
@@ -916,9 +1120,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -935,42 +1136,10 @@
     <t>Observation.dataAbsentReason.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1911,12 +2080,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1924,7 +2093,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1938,7 +2107,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2465,10 +2634,10 @@
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>107</v>
@@ -2479,9 +2648,7 @@
       <c r="M5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>82</v>
@@ -2530,7 +2697,7 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2542,7 +2709,7 @@
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2554,7 +2721,7 @@
         <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>82</v>
@@ -2572,14 +2739,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2591,16 +2758,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2626,43 +2793,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2674,7 +2841,7 @@
         <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>82</v>
@@ -2685,14 +2852,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2708,10 +2875,10 @@
         <v>82</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>124</v>
@@ -2794,7 +2961,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2805,21 +2972,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>82</v>
@@ -2828,19 +2995,19 @@
         <v>82</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2890,19 +3057,19 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2914,7 +3081,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2925,21 +3092,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>82</v>
@@ -2948,19 +3115,19 @@
         <v>82</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3010,19 +3177,19 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -3034,7 +3201,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3045,14 +3212,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3065,26 +3232,24 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3132,7 +3297,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3144,7 +3309,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3156,7 +3321,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3167,10 +3332,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3193,18 +3358,18 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3228,13 +3393,13 @@
         <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>82</v>
@@ -3252,7 +3417,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3267,19 +3432,19 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3287,14 +3452,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3313,18 +3478,18 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3348,13 +3513,13 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
@@ -3372,7 +3537,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3387,16 +3552,16 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3407,42 +3572,42 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3492,13 +3657,13 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
@@ -3507,16 +3672,16 @@
         <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3527,10 +3692,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3538,7 +3703,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
@@ -3547,26 +3712,24 @@
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3590,13 +3753,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3614,10 +3777,10 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3629,19 +3792,19 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3649,21 +3812,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3675,20 +3838,18 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3712,13 +3873,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3736,13 +3897,13 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
@@ -3760,10 +3921,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3771,21 +3932,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3794,23 +3955,21 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3819,7 +3978,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3834,13 +3993,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3858,45 +4017,45 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3907,7 +4066,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3916,23 +4075,19 @@
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -3968,46 +4123,44 @@
         <v>82</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4015,12 +4168,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4029,7 +4184,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4038,20 +4193,18 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4100,7 +4253,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4112,7 +4265,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4121,13 +4274,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4135,14 +4288,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4158,23 +4313,19 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4222,34 +4373,34 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4257,14 +4408,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4280,23 +4433,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4344,34 +4493,34 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4379,44 +4528,46 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4464,19 +4615,19 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -4485,13 +4636,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4499,10 +4650,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4525,17 +4676,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4584,7 +4735,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4599,19 +4750,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4619,21 +4770,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4645,19 +4796,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4706,56 +4855,56 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4764,23 +4913,21 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4804,13 +4951,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4828,31 +4975,31 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>136</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>291</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4863,10 +5010,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>292</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4874,7 +5021,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>93</v>
@@ -4883,22 +5030,26 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>272</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4922,13 +5073,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4946,10 +5097,10 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>93</v>
@@ -4958,22 +5109,22 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4981,14 +5132,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5007,18 +5158,20 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>139</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5042,31 +5195,31 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>302</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5078,7 +5231,7 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5090,10 +5243,10 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5101,21 +5254,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5127,19 +5280,19 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5149,7 +5302,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5164,13 +5317,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5188,13 +5341,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5203,30 +5356,30 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5246,19 +5399,23 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5306,7 +5463,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5318,22 +5475,22 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5341,14 +5498,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5364,19 +5521,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>139</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>140</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5414,19 +5571,19 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5438,7 +5595,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5447,13 +5604,13 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5461,18 +5618,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>
@@ -5487,19 +5644,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>301</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5548,7 +5705,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5563,19 +5720,19 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5583,14 +5740,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5609,18 +5766,20 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5668,7 +5827,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5683,19 +5842,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5703,10 +5862,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5714,7 +5873,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -5729,18 +5888,18 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5788,7 +5947,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5809,13 +5968,13 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5823,10 +5982,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5837,7 +5996,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5849,17 +6008,17 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5908,13 +6067,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -5923,19 +6082,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5943,10 +6102,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5969,19 +6128,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>344</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6030,7 +6189,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6039,7 +6198,7 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
@@ -6048,27 +6207,27 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6088,22 +6247,22 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6128,13 +6287,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6152,7 +6311,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6161,7 +6320,7 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6173,10 +6332,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>192</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6187,21 +6346,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6213,20 +6372,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>362</v>
+        <v>108</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6250,13 +6405,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6274,49 +6429,49 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>370</v>
+        <v>111</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6335,20 +6490,18 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>373</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>374</v>
+        <v>115</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>375</v>
+        <v>116</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6384,19 +6537,19 @@
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>372</v>
+        <v>121</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6408,7 +6561,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6417,10 +6570,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>379</v>
+        <v>111</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6431,10 +6584,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6445,7 +6598,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6454,21 +6607,23 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6492,13 +6647,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6516,13 +6671,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6534,27 +6689,27 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6562,7 +6717,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
@@ -6577,20 +6732,16 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>391</v>
+        <v>108</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6614,11 +6765,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6636,7 +6789,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6648,7 +6801,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6657,10 +6810,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>397</v>
+        <v>111</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6671,21 +6824,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6697,16 +6850,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>399</v>
+        <v>114</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>115</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>116</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>117</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6744,57 +6897,57 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>121</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>111</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6802,7 +6955,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
@@ -6814,21 +6967,23 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>408</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6876,7 +7031,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6894,27 +7049,27 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6925,7 +7080,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6934,23 +7089,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>417</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6998,19 +7151,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>422</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7019,10 +7172,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>423</v>
+        <v>381</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>424</v>
+        <v>382</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7033,10 +7186,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7044,7 +7197,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7056,19 +7209,21 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>272</v>
+        <v>169</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>293</v>
+        <v>384</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>294</v>
+        <v>385</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7116,7 +7271,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>295</v>
+        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7128,7 +7283,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7137,10 +7292,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>296</v>
+        <v>389</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7151,21 +7306,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7174,21 +7329,21 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>140</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7236,19 +7391,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>302</v>
+        <v>394</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7257,10 +7412,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>296</v>
+        <v>396</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7271,45 +7426,45 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>398</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>142</v>
+        <v>401</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>148</v>
+        <v>402</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7358,19 +7513,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7379,10 +7534,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>136</v>
+        <v>405</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7393,10 +7548,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7416,19 +7571,23 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>433</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7476,7 +7635,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7485,7 +7644,7 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>105</v>
@@ -7497,10 +7656,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7511,21 +7670,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7537,16 +7696,20 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>433</v>
+        <v>259</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7570,13 +7733,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7594,16 +7757,16 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7612,27 +7775,27 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7643,7 +7806,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7655,19 +7818,19 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>427</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7692,13 +7855,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7716,13 +7879,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7734,13 +7897,13 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>370</v>
+        <v>433</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7751,10 +7914,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7765,7 +7928,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7777,20 +7940,18 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7814,13 +7975,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7838,13 +7999,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7856,27 +8017,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>442</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7884,7 +8045,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -7899,17 +8060,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>460</v>
+        <v>259</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7934,13 +8097,11 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7958,7 +8119,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7979,10 +8140,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7993,10 +8154,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8019,15 +8180,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>272</v>
+        <v>453</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8076,7 +8239,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8094,27 +8257,27 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8125,7 +8288,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8134,19 +8297,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8196,13 +8359,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8214,27 +8377,27 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8245,7 +8408,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8254,21 +8417,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8316,7 +8481,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8328,7 +8493,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>476</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8337,10 +8502,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8351,10 +8516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8365,7 +8530,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8374,23 +8539,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>417</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>483</v>
+        <v>108</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8438,19 +8599,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>482</v>
+        <v>110</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8459,10 +8620,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>488</v>
+        <v>111</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8473,21 +8634,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8499,15 +8660,17 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>272</v>
+        <v>114</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>293</v>
+        <v>115</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8556,19 +8719,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>295</v>
+        <v>121</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8580,7 +8743,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>296</v>
+        <v>111</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8591,14 +8754,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>138</v>
+        <v>482</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8611,24 +8774,26 @@
         <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>140</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>298</v>
+        <v>484</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8676,7 +8841,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>302</v>
+        <v>485</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8688,7 +8853,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8700,7 +8865,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8711,46 +8876,42 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>487</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>429</v>
+        <v>488</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8798,19 +8959,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>431</v>
+        <v>486</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -8819,10 +8980,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>136</v>
+        <v>492</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8833,10 +8994,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8844,7 +9005,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
@@ -8856,23 +9017,19 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>191</v>
+        <v>487</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N58" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -8896,13 +9053,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8920,16 +9077,16 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -8938,16 +9095,16 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="AO58" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8978,22 +9135,22 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>500</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>276</v>
+        <v>501</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9018,13 +9175,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9060,27 +9217,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>279</v>
+        <v>505</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>280</v>
+        <v>424</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9091,7 +9248,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9103,19 +9260,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>286</v>
+        <v>510</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9140,13 +9297,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>287</v>
+        <v>159</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>288</v>
+        <v>511</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>289</v>
+        <v>512</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9164,16 +9321,16 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9182,13 +9339,13 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>136</v>
+        <v>505</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>291</v>
+        <v>424</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9199,21 +9356,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9225,19 +9382,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>514</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>362</v>
+        <v>515</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>365</v>
+        <v>517</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9262,13 +9417,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9286,13 +9441,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9304,27 +9459,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>370</v>
+        <v>518</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9335,7 +9490,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9347,20 +9502,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9408,13 +9559,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9429,15 +9580,1347 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP62" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1416,7 +1416,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/1.2.250.1.213.1.1.5.789</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-technique-biologie-cisis</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2108,7 +2108,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.64453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.12109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$73</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1907,6 +1910,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2254,7 +2272,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2374,7 +2392,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -2494,7 +2512,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -2612,7 +2630,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -2730,7 +2748,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -2850,7 +2868,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>123</v>
       </c>
@@ -2970,7 +2988,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>128</v>
       </c>
@@ -3090,7 +3108,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -3210,7 +3228,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -3330,7 +3348,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3450,7 +3468,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>155</v>
       </c>
@@ -3570,7 +3588,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -3690,7 +3708,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3810,7 +3828,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>177</v>
       </c>
@@ -3930,7 +3948,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>185</v>
       </c>
@@ -4050,7 +4068,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>193</v>
       </c>
@@ -4166,7 +4184,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>197</v>
       </c>
@@ -4286,7 +4304,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>202</v>
       </c>
@@ -4406,7 +4424,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>208</v>
       </c>
@@ -4526,7 +4544,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>213</v>
       </c>
@@ -4648,7 +4666,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>218</v>
       </c>
@@ -4768,7 +4786,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>227</v>
       </c>
@@ -4888,7 +4906,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>236</v>
       </c>
@@ -5008,7 +5026,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>245</v>
       </c>
@@ -5130,7 +5148,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>258</v>
       </c>
@@ -5252,7 +5270,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>268</v>
       </c>
@@ -5374,7 +5392,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>283</v>
       </c>
@@ -5496,7 +5514,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>293</v>
       </c>
@@ -5616,7 +5634,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>299</v>
       </c>
@@ -5738,7 +5756,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>310</v>
       </c>
@@ -5860,7 +5878,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>321</v>
       </c>
@@ -5980,7 +5998,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>328</v>
       </c>
@@ -6100,7 +6118,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>337</v>
       </c>
@@ -6222,7 +6240,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>347</v>
       </c>
@@ -6344,7 +6362,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>356</v>
       </c>
@@ -6462,7 +6480,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>357</v>
       </c>
@@ -6582,7 +6600,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>358</v>
       </c>
@@ -6704,7 +6722,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>366</v>
       </c>
@@ -6822,7 +6840,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>367</v>
       </c>
@@ -6942,7 +6960,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>368</v>
       </c>
@@ -7064,7 +7082,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>376</v>
       </c>
@@ -7184,7 +7202,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>383</v>
       </c>
@@ -7304,7 +7322,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>390</v>
       </c>
@@ -7424,7 +7442,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>397</v>
       </c>
@@ -7546,7 +7564,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>406</v>
       </c>
@@ -7668,7 +7686,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>414</v>
       </c>
@@ -7790,7 +7808,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>426</v>
       </c>
@@ -7912,7 +7930,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>434</v>
       </c>
@@ -8051,7 +8069,7 @@
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8152,7 +8170,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>452</v>
       </c>
@@ -8272,7 +8290,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>461</v>
       </c>
@@ -8392,7 +8410,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>470</v>
       </c>
@@ -8514,7 +8532,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>479</v>
       </c>
@@ -8632,7 +8650,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>480</v>
       </c>
@@ -8752,7 +8770,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>481</v>
       </c>
@@ -8874,7 +8892,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>486</v>
       </c>
@@ -8992,7 +9010,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>493</v>
       </c>
@@ -9110,7 +9128,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>497</v>
       </c>
@@ -9232,7 +9250,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>506</v>
       </c>
@@ -9354,7 +9372,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>513</v>
       </c>
@@ -9474,7 +9492,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>519</v>
       </c>
@@ -9592,7 +9610,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>523</v>
       </c>
@@ -9712,7 +9730,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>530</v>
       </c>
@@ -9832,7 +9850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>536</v>
       </c>
@@ -9954,7 +9972,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>543</v>
       </c>
@@ -10072,7 +10090,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>544</v>
       </c>
@@ -10192,7 +10210,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>545</v>
       </c>
@@ -10314,7 +10332,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>546</v>
       </c>
@@ -10436,7 +10454,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>551</v>
       </c>
@@ -10558,7 +10576,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>556</v>
       </c>
@@ -10680,7 +10698,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>560</v>
       </c>
@@ -10802,7 +10820,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>561</v>
       </c>
@@ -10925,6 +10943,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP73">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI72">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1491,7 +1491,7 @@
 </t>
   </si>
   <si>
-    <t>Provides guide for interpretation</t>
+    <t>Associer la mesure à l'intervalle de référence est fortement recommandé pour interpréter le résultat par rapport à la norme, qui peut varier selon de nombreux critères : la méthode d'analyse, l'age, le sexe, ...</t>
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
@@ -8410,7 +8410,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>470</v>
       </c>
@@ -8429,7 +8429,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8426,7 +8426,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>94</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-aspect.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>MesFrObservationCholesterolAspect</t>
+    <t>MesObservationCholesterolAspect</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -667,20 +667,21 @@
 </t>
   </si>
   <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+    <t>Observation.extension:mes-original-data</t>
+  </si>
+  <si>
+    <t>mes-original-data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-original-data}
 </t>
   </si>
   <si>
     <t>Valeur d'origine de la donnée. Cette extension est présente uniquement si le résultat contenu dans Observation.value provient d'une conversion (par ex. g/L converti en mmol/L)</t>
   </si>
   <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
+    <t>Extension permettant de renseigner la donnée originale. 
+Dans le cas où une conversion d'unité a été effectuée sur la valeur de la mesure, cette extension permet de conserver la valeur originale telle que mesurée par le dispositif.</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
